--- a/Result/profitability/1802.xlsx
+++ b/Result/profitability/1802.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02375000000000001</v>
+        <v>0.07874999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>12.36875</v>
+        <v>14.85875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,16 +681,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03999999999999999</v>
+        <v>0.09749999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>14.245</v>
+        <v>15.81125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09875</v>
+        <v>0.17</v>
       </c>
       <c r="N4" t="n">
-        <v>14.74625</v>
+        <v>16.29375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1</v>
+        <v>0.1925</v>
       </c>
       <c r="N5" t="n">
-        <v>13.8025</v>
+        <v>15.46875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1075</v>
+        <v>0.15</v>
       </c>
       <c r="N6" t="n">
-        <v>13.20875</v>
+        <v>14.6675</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09</v>
+        <v>0.12875</v>
       </c>
       <c r="N7" t="n">
-        <v>12.975</v>
+        <v>14.1825</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="N8" t="n">
-        <v>13.50375</v>
+        <v>14.01625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>12062</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9248</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1524</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.64%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-195</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1330</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1267</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.004999999999999991</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.88125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.099999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2132085283411336</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.466666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
